--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/total.trans.carotene.natif/RANDOMSEARCH_DETAILS_total.trans.carotene.natif.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/total.trans.carotene.natif/RANDOMSEARCH_DETAILS_total.trans.carotene.natif.xlsx
@@ -413,9 +413,4084 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Compose</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ID_Pretraitement</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Code_R_Pretraitement</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Meilleurs_Hyperparam_RF</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>R2cv</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>RMSEC</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>RMSECV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('snv',''), list('sder',c(1,3,5))</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.3113</v>
+      </c>
+      <c r="G2" t="n">
+        <v>140.7441</v>
+      </c>
+      <c r="H2" t="n">
+        <v>370.164</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9875</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.3344</v>
+      </c>
+      <c r="G3" t="n">
+        <v>129.7832</v>
+      </c>
+      <c r="H3" t="n">
+        <v>383.6347</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1))</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.4078</v>
+      </c>
+      <c r="G4" t="n">
+        <v>151.7454</v>
+      </c>
+      <c r="H4" t="n">
+        <v>423.6192</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,700,1)),list('snv','')</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.8381</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.0031</v>
+      </c>
+      <c r="G5" t="n">
+        <v>398.576</v>
+      </c>
+      <c r="H5" t="n">
+        <v>664.4082</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,750,1)),list('snv','')</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8228</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.9864</v>
+      </c>
+      <c r="G6" t="n">
+        <v>412.1131</v>
+      </c>
+      <c r="H6" t="n">
+        <v>658.8523</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1000,1)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.4213</v>
+      </c>
+      <c r="G7" t="n">
+        <v>174.3909</v>
+      </c>
+      <c r="H7" t="n">
+        <v>430.6083</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9504</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.4168</v>
+      </c>
+      <c r="G8" t="n">
+        <v>218.2784</v>
+      </c>
+      <c r="H8" t="n">
+        <v>428.3029</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1200,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9885</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="G9" t="n">
+        <v>128.9592</v>
+      </c>
+      <c r="H9" t="n">
+        <v>368.1915</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9715</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.443</v>
+      </c>
+      <c r="G10" t="n">
+        <v>174.2967</v>
+      </c>
+      <c r="H10" t="n">
+        <v>441.5528</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9777</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.4504</v>
+      </c>
+      <c r="G11" t="n">
+        <v>158.0648</v>
+      </c>
+      <c r="H11" t="n">
+        <v>445.2347</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9497</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.4494</v>
+      </c>
+      <c r="G12" t="n">
+        <v>220.1589</v>
+      </c>
+      <c r="H12" t="n">
+        <v>444.7286</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9383</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.4508</v>
+      </c>
+      <c r="G13" t="n">
+        <v>240.2028</v>
+      </c>
+      <c r="H13" t="n">
+        <v>445.4274</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9364</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.4492</v>
+      </c>
+      <c r="G14" t="n">
+        <v>243.4965</v>
+      </c>
+      <c r="H14" t="n">
+        <v>444.645</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9485</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.4506</v>
+      </c>
+      <c r="G15" t="n">
+        <v>222.9272</v>
+      </c>
+      <c r="H15" t="n">
+        <v>445.3399</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9362</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.4559</v>
+      </c>
+      <c r="G16" t="n">
+        <v>244.363</v>
+      </c>
+      <c r="H16" t="n">
+        <v>447.95</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9364</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.4543</v>
+      </c>
+      <c r="G17" t="n">
+        <v>243.8387</v>
+      </c>
+      <c r="H17" t="n">
+        <v>447.1251</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 5))</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9843</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.3264</v>
+      </c>
+      <c r="G18" t="n">
+        <v>130.0626</v>
+      </c>
+      <c r="H18" t="n">
+        <v>378.9852</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9819</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.3158</v>
+      </c>
+      <c r="G19" t="n">
+        <v>135.9049</v>
+      </c>
+      <c r="H19" t="n">
+        <v>372.8124</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9795</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.3173</v>
+      </c>
+      <c r="G20" t="n">
+        <v>145.4921</v>
+      </c>
+      <c r="H20" t="n">
+        <v>373.6858</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9854000000000001</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.3079</v>
+      </c>
+      <c r="G21" t="n">
+        <v>126.8036</v>
+      </c>
+      <c r="H21" t="n">
+        <v>368.0905</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>21</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9858</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.2992</v>
+      </c>
+      <c r="G22" t="n">
+        <v>125.6142</v>
+      </c>
+      <c r="H22" t="n">
+        <v>362.8445</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.3119</v>
+      </c>
+      <c r="G23" t="n">
+        <v>128.1761</v>
+      </c>
+      <c r="H23" t="n">
+        <v>370.5051</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.3035</v>
+      </c>
+      <c r="G24" t="n">
+        <v>150.1747</v>
+      </c>
+      <c r="H24" t="n">
+        <v>365.4631</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 35))</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9841</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.3027</v>
+      </c>
+      <c r="G25" t="n">
+        <v>130.2113</v>
+      </c>
+      <c r="H25" t="n">
+        <v>365.0037</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 5))</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="G26" t="n">
+        <v>126.3311</v>
+      </c>
+      <c r="H26" t="n">
+        <v>372.3351</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9849</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.3264</v>
+      </c>
+      <c r="G27" t="n">
+        <v>131.0795</v>
+      </c>
+      <c r="H27" t="n">
+        <v>378.9793</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.3106</v>
+      </c>
+      <c r="G28" t="n">
+        <v>131.4122</v>
+      </c>
+      <c r="H28" t="n">
+        <v>369.7393</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>28</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.3227</v>
+      </c>
+      <c r="G29" t="n">
+        <v>131.0279</v>
+      </c>
+      <c r="H29" t="n">
+        <v>376.8445</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>29</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9849</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.3101</v>
+      </c>
+      <c r="G30" t="n">
+        <v>129.2158</v>
+      </c>
+      <c r="H30" t="n">
+        <v>369.4271</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9849</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.3145</v>
+      </c>
+      <c r="G31" t="n">
+        <v>129.1021</v>
+      </c>
+      <c r="H31" t="n">
+        <v>372.0269</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>31</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9855</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.3044</v>
+      </c>
+      <c r="G32" t="n">
+        <v>127.3325</v>
+      </c>
+      <c r="H32" t="n">
+        <v>366.0345</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>32</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 35))</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9856</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.3133</v>
+      </c>
+      <c r="G33" t="n">
+        <v>127.051</v>
+      </c>
+      <c r="H33" t="n">
+        <v>371.3089</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>33</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.9765</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.3586</v>
+      </c>
+      <c r="G34" t="n">
+        <v>168.4107</v>
+      </c>
+      <c r="H34" t="n">
+        <v>397.2605</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>34</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9868</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.3466</v>
+      </c>
+      <c r="G35" t="n">
+        <v>133.9053</v>
+      </c>
+      <c r="H35" t="n">
+        <v>390.5407</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>35</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.324</v>
+      </c>
+      <c r="G36" t="n">
+        <v>129.3663</v>
+      </c>
+      <c r="H36" t="n">
+        <v>377.6252</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>36</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.9876</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.3175</v>
+      </c>
+      <c r="G37" t="n">
+        <v>124.7023</v>
+      </c>
+      <c r="H37" t="n">
+        <v>373.8045</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>37</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.9802</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.3053</v>
+      </c>
+      <c r="G38" t="n">
+        <v>156.887</v>
+      </c>
+      <c r="H38" t="n">
+        <v>366.5286</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>38</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.9861</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.3147</v>
+      </c>
+      <c r="G39" t="n">
+        <v>126.6765</v>
+      </c>
+      <c r="H39" t="n">
+        <v>372.1749</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>39</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 35))</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.9854000000000001</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.3174</v>
+      </c>
+      <c r="G40" t="n">
+        <v>133.1028</v>
+      </c>
+      <c r="H40" t="n">
+        <v>373.7714</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>40</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9769</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.3589</v>
+      </c>
+      <c r="G41" t="n">
+        <v>167.9518</v>
+      </c>
+      <c r="H41" t="n">
+        <v>397.4093</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>41</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.9867</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.3472</v>
+      </c>
+      <c r="G42" t="n">
+        <v>134.4413</v>
+      </c>
+      <c r="H42" t="n">
+        <v>390.8835</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>42</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.9871</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.3266</v>
+      </c>
+      <c r="G43" t="n">
+        <v>129.1184</v>
+      </c>
+      <c r="H43" t="n">
+        <v>379.147</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>43</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0.9869</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1.3121</v>
+      </c>
+      <c r="G44" t="n">
+        <v>127.8132</v>
+      </c>
+      <c r="H44" t="n">
+        <v>370.6106</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>44</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.9801</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1.2993</v>
+      </c>
+      <c r="G45" t="n">
+        <v>156.2138</v>
+      </c>
+      <c r="H45" t="n">
+        <v>362.9135</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>45</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0.9862</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.3181</v>
+      </c>
+      <c r="G46" t="n">
+        <v>126.0829</v>
+      </c>
+      <c r="H46" t="n">
+        <v>374.1761</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>46</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 35))</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0.9782</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.3237</v>
+      </c>
+      <c r="G47" t="n">
+        <v>158.3174</v>
+      </c>
+      <c r="H47" t="n">
+        <v>377.4575</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>47</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1400,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0.9859</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.3407</v>
+      </c>
+      <c r="G48" t="n">
+        <v>135.8183</v>
+      </c>
+      <c r="H48" t="n">
+        <v>387.2409</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>48</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(40,1300,1)),list('snv',''),list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0.9868</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.3173</v>
+      </c>
+      <c r="G49" t="n">
+        <v>131.0246</v>
+      </c>
+      <c r="H49" t="n">
+        <v>373.697</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>49</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0.9303</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1.8437</v>
+      </c>
+      <c r="G50" t="n">
+        <v>312.4229</v>
+      </c>
+      <c r="H50" t="n">
+        <v>609.3537</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>50</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(1,3,11))</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0.8963</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1.881</v>
+      </c>
+      <c r="G51" t="n">
+        <v>369.8412</v>
+      </c>
+      <c r="H51" t="n">
+        <v>622.6793</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>51</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0.8874</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.8833</v>
+      </c>
+      <c r="G52" t="n">
+        <v>374.7844</v>
+      </c>
+      <c r="H52" t="n">
+        <v>623.4897999999999</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>52</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0.9127</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.8622</v>
+      </c>
+      <c r="G53" t="n">
+        <v>356.8295</v>
+      </c>
+      <c r="H53" t="n">
+        <v>616.0087</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>53</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(2,3,21))</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0.9006999999999999</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.8379</v>
+      </c>
+      <c r="G54" t="n">
+        <v>362.0448</v>
+      </c>
+      <c r="H54" t="n">
+        <v>607.2488</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>54</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,20,1)),list('snv',''),list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.9205</v>
+      </c>
+      <c r="G55" t="n">
+        <v>233.3946</v>
+      </c>
+      <c r="H55" t="n">
+        <v>636.4865</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>55</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,20,1)),list('snv',''),list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0.9764</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.9141</v>
+      </c>
+      <c r="G56" t="n">
+        <v>233.3864</v>
+      </c>
+      <c r="H56" t="n">
+        <v>634.2611000000001</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>56</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,650,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0.9113</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1.902</v>
+      </c>
+      <c r="G57" t="n">
+        <v>357.056</v>
+      </c>
+      <c r="H57" t="n">
+        <v>630.0482</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>57</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,15))</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0.8209</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.9874</v>
+      </c>
+      <c r="G58" t="n">
+        <v>412.9541</v>
+      </c>
+      <c r="H58" t="n">
+        <v>659.1869</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>58</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,21))</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0.8274</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1.9887</v>
+      </c>
+      <c r="G59" t="n">
+        <v>408.9831</v>
+      </c>
+      <c r="H59" t="n">
+        <v>659.6507</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>59</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,25))</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0.8288</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1.9812</v>
+      </c>
+      <c r="G60" t="n">
+        <v>407.2439</v>
+      </c>
+      <c r="H60" t="n">
+        <v>657.1375</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>60</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,31))</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0.8282</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1.9925</v>
+      </c>
+      <c r="G61" t="n">
+        <v>405.9075</v>
+      </c>
+      <c r="H61" t="n">
+        <v>660.8886</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>61</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,11))</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0.838</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1.927</v>
+      </c>
+      <c r="G62" t="n">
+        <v>418.1797</v>
+      </c>
+      <c r="H62" t="n">
+        <v>638.7118</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>62</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0.8354</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1.9225</v>
+      </c>
+      <c r="G63" t="n">
+        <v>419.0805</v>
+      </c>
+      <c r="H63" t="n">
+        <v>637.1592000000001</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>63</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,21))</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0.8287</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1.9186</v>
+      </c>
+      <c r="G64" t="n">
+        <v>419.602</v>
+      </c>
+      <c r="H64" t="n">
+        <v>635.8348999999999</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>64</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,31))</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0.8227</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1.9343</v>
+      </c>
+      <c r="G65" t="n">
+        <v>421.583</v>
+      </c>
+      <c r="H65" t="n">
+        <v>641.2296</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>65</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0.9016</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.9156</v>
+      </c>
+      <c r="G66" t="n">
+        <v>364.3609</v>
+      </c>
+      <c r="H66" t="n">
+        <v>634.7954</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>66</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1000,700,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0.8952</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1.8947</v>
+      </c>
+      <c r="G67" t="n">
+        <v>372.2366</v>
+      </c>
+      <c r="H67" t="n">
+        <v>627.5069</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>67</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1000,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0.8956</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1.9194</v>
+      </c>
+      <c r="G68" t="n">
+        <v>380.4722</v>
+      </c>
+      <c r="H68" t="n">
+        <v>636.0913</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>72</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,11)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0.9802</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1.3269</v>
+      </c>
+      <c r="G69" t="n">
+        <v>147.2465</v>
+      </c>
+      <c r="H69" t="n">
+        <v>379.3111</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>73</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0.9821</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1.2998</v>
+      </c>
+      <c r="G70" t="n">
+        <v>139.5488</v>
+      </c>
+      <c r="H70" t="n">
+        <v>363.2622</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>74</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0.9839</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1.3323</v>
+      </c>
+      <c r="G71" t="n">
+        <v>133.6539</v>
+      </c>
+      <c r="H71" t="n">
+        <v>382.3925</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>75</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1.3141</v>
+      </c>
+      <c r="G72" t="n">
+        <v>128.1703</v>
+      </c>
+      <c r="H72" t="n">
+        <v>371.7926</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>76</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1.3573</v>
+      </c>
+      <c r="G73" t="n">
+        <v>140.5687</v>
+      </c>
+      <c r="H73" t="n">
+        <v>396.5206</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>77</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>0.9857</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1.3243</v>
+      </c>
+      <c r="G74" t="n">
+        <v>132.9789</v>
+      </c>
+      <c r="H74" t="n">
+        <v>377.7863</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>78</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>0.9827</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1.3891</v>
+      </c>
+      <c r="G75" t="n">
+        <v>138.5767</v>
+      </c>
+      <c r="H75" t="n">
+        <v>413.7852</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>79</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3')</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>0.9827</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1.3891</v>
+      </c>
+      <c r="G76" t="n">
+        <v>138.5767</v>
+      </c>
+      <c r="H76" t="n">
+        <v>413.7852</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>80</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>0.8512999999999999</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1.9257</v>
+      </c>
+      <c r="G77" t="n">
+        <v>395.3523</v>
+      </c>
+      <c r="H77" t="n">
+        <v>638.2849</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>81</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0.8555</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1.9321</v>
+      </c>
+      <c r="G78" t="n">
+        <v>393.5737</v>
+      </c>
+      <c r="H78" t="n">
+        <v>640.4891</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>82</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0.8537</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1.9298</v>
+      </c>
+      <c r="G79" t="n">
+        <v>394.4773</v>
+      </c>
+      <c r="H79" t="n">
+        <v>639.6693</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>83</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0.8556</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1.9305</v>
+      </c>
+      <c r="G80" t="n">
+        <v>392.8552</v>
+      </c>
+      <c r="H80" t="n">
+        <v>639.9406</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>84</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0.8983</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1.9203</v>
+      </c>
+      <c r="G81" t="n">
+        <v>366.4063</v>
+      </c>
+      <c r="H81" t="n">
+        <v>636.4066</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>85</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>0.9213</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1.9218</v>
+      </c>
+      <c r="G82" t="n">
+        <v>322.5342</v>
+      </c>
+      <c r="H82" t="n">
+        <v>636.9181</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>86</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0.9823</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1.3891</v>
+      </c>
+      <c r="G83" t="n">
+        <v>135.7459</v>
+      </c>
+      <c r="H83" t="n">
+        <v>413.7923</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>87</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0.9849</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1.386</v>
+      </c>
+      <c r="G84" t="n">
+        <v>128.8765</v>
+      </c>
+      <c r="H84" t="n">
+        <v>412.1432</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>88</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>0.9818</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1.3877</v>
+      </c>
+      <c r="G85" t="n">
+        <v>137.3948</v>
+      </c>
+      <c r="H85" t="n">
+        <v>413.0682</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>89</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0.9858</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1.3111</v>
+      </c>
+      <c r="G86" t="n">
+        <v>122.6694</v>
+      </c>
+      <c r="H86" t="n">
+        <v>370.0113</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>90</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>0.9807</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1.3215</v>
+      </c>
+      <c r="G87" t="n">
+        <v>142.8131</v>
+      </c>
+      <c r="H87" t="n">
+        <v>376.1407</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>91</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0.9861</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1.3212</v>
+      </c>
+      <c r="G88" t="n">
+        <v>122.1792</v>
+      </c>
+      <c r="H88" t="n">
+        <v>375.95</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>92</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0.9855</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1.3189</v>
+      </c>
+      <c r="G89" t="n">
+        <v>124.18</v>
+      </c>
+      <c r="H89" t="n">
+        <v>374.6143</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>93</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>0.9871</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1.3267</v>
+      </c>
+      <c r="G90" t="n">
+        <v>129.1657</v>
+      </c>
+      <c r="H90" t="n">
+        <v>379.1697</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>94</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>0.9869</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1.3121</v>
+      </c>
+      <c r="G91" t="n">
+        <v>127.8215</v>
+      </c>
+      <c r="H91" t="n">
+        <v>370.593</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>95</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>0.9861</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1.3212</v>
+      </c>
+      <c r="G92" t="n">
+        <v>122.1792</v>
+      </c>
+      <c r="H92" t="n">
+        <v>375.95</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>96</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>0.9869</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1.3121</v>
+      </c>
+      <c r="G93" t="n">
+        <v>127.8215</v>
+      </c>
+      <c r="H93" t="n">
+        <v>370.593</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>97</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1.4078</v>
+      </c>
+      <c r="G94" t="n">
+        <v>151.7454</v>
+      </c>
+      <c r="H94" t="n">
+        <v>423.6192</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>98</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>0.9294</v>
+      </c>
+      <c r="F95" t="n">
+        <v>2.0964</v>
+      </c>
+      <c r="G95" t="n">
+        <v>337.3206</v>
+      </c>
+      <c r="H95" t="n">
+        <v>694.6193</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>99</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>0.9805</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1.4113</v>
+      </c>
+      <c r="G96" t="n">
+        <v>154.2423</v>
+      </c>
+      <c r="H96" t="n">
+        <v>425.4429</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>100</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>0.9806</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1.4063</v>
+      </c>
+      <c r="G97" t="n">
+        <v>155.0043</v>
+      </c>
+      <c r="H97" t="n">
+        <v>422.851</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>101</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 5))</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>0.9776</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="G98" t="n">
+        <v>154.5058</v>
+      </c>
+      <c r="H98" t="n">
+        <v>378.1848</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>102</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>0.9787</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1.2945</v>
+      </c>
+      <c r="G99" t="n">
+        <v>147.4648</v>
+      </c>
+      <c r="H99" t="n">
+        <v>359.9936</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>103</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>0.9777</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1.3135</v>
+      </c>
+      <c r="G100" t="n">
+        <v>150.8356</v>
+      </c>
+      <c r="H100" t="n">
+        <v>371.4181</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>104</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>0.9775</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1.306</v>
+      </c>
+      <c r="G101" t="n">
+        <v>151.8248</v>
+      </c>
+      <c r="H101" t="n">
+        <v>366.9511</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>105</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>0.9771</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1.3163</v>
+      </c>
+      <c r="G102" t="n">
+        <v>154.4196</v>
+      </c>
+      <c r="H102" t="n">
+        <v>373.1085</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>106</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 5))</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="G103" t="n">
+        <v>132.9983</v>
+      </c>
+      <c r="H103" t="n">
+        <v>378.1728</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>107</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>0.9837</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1.3206</v>
+      </c>
+      <c r="G104" t="n">
+        <v>136.7633</v>
+      </c>
+      <c r="H104" t="n">
+        <v>375.6284</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>108</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G105" t="n">
+        <v>130.8418</v>
+      </c>
+      <c r="H105" t="n">
+        <v>357.2375</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>109</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>0.9836</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="G106" t="n">
+        <v>132.2536</v>
+      </c>
+      <c r="H106" t="n">
+        <v>351.6306</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>110</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>0.9835</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1.2984</v>
+      </c>
+      <c r="G107" t="n">
+        <v>133.0067</v>
+      </c>
+      <c r="H107" t="n">
+        <v>362.3866</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>111</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>0.9786</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1.3995</v>
+      </c>
+      <c r="G108" t="n">
+        <v>166.0339</v>
+      </c>
+      <c r="H108" t="n">
+        <v>419.2859</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>112</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1.3647</v>
+      </c>
+      <c r="G109" t="n">
+        <v>138.8048</v>
+      </c>
+      <c r="H109" t="n">
+        <v>400.6358</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>113</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>0.9867</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1.3317</v>
+      </c>
+      <c r="G110" t="n">
+        <v>132.1723</v>
+      </c>
+      <c r="H110" t="n">
+        <v>382.0609</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>114</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>0.9862</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1.3268</v>
+      </c>
+      <c r="G111" t="n">
+        <v>130.3356</v>
+      </c>
+      <c r="H111" t="n">
+        <v>379.2433</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>115</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1.3975</v>
+      </c>
+      <c r="G112" t="n">
+        <v>165.9844</v>
+      </c>
+      <c r="H112" t="n">
+        <v>418.2393</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>116</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>0.9801</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1.3651</v>
+      </c>
+      <c r="G113" t="n">
+        <v>169.2929</v>
+      </c>
+      <c r="H113" t="n">
+        <v>400.8277</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>117</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>0.9868</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1.3304</v>
+      </c>
+      <c r="G114" t="n">
+        <v>131.5674</v>
+      </c>
+      <c r="H114" t="n">
+        <v>381.3241</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>118</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1.3292</v>
+      </c>
+      <c r="G115" t="n">
+        <v>130.3998</v>
+      </c>
+      <c r="H115" t="n">
+        <v>380.6561</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>119</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>0.9699</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1.9243</v>
+      </c>
+      <c r="G116" t="n">
+        <v>239.0892</v>
+      </c>
+      <c r="H116" t="n">
+        <v>637.7876</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>120</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,21))</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>0.9293</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.9494</v>
+      </c>
+      <c r="G117" t="n">
+        <v>316.9833</v>
+      </c>
+      <c r="H117" t="n">
+        <v>646.3871</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>121</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G118" t="n">
+        <v>130.8418</v>
+      </c>
+      <c r="H118" t="n">
+        <v>357.2375</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>122</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>0.9801</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1.3651</v>
+      </c>
+      <c r="G119" t="n">
+        <v>169.2929</v>
+      </c>
+      <c r="H119" t="n">
+        <v>400.8277</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>123</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.3916</v>
+      </c>
+      <c r="G120" t="n">
+        <v>179.321</v>
+      </c>
+      <c r="H120" t="n">
+        <v>415.1462</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>124</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3')</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1.3916</v>
+      </c>
+      <c r="G121" t="n">
+        <v>179.321</v>
+      </c>
+      <c r="H121" t="n">
+        <v>415.1462</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>125</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>0.9858</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1.2928</v>
+      </c>
+      <c r="G122" t="n">
+        <v>125.518</v>
+      </c>
+      <c r="H122" t="n">
+        <v>358.957</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>126</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1.3661</v>
+      </c>
+      <c r="G123" t="n">
+        <v>169.3909</v>
+      </c>
+      <c r="H123" t="n">
+        <v>401.3778</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>127</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3'), list('sder',c(2,4,31))</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>0.9872</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1.332</v>
+      </c>
+      <c r="G124" t="n">
+        <v>130.0281</v>
+      </c>
+      <c r="H124" t="n">
+        <v>382.2485</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>172</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>list('snv',''),list('sder',c(1,3,9)),list('red',c(10,10,1))</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>0.9814000000000001</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1.3156</v>
+      </c>
+      <c r="G125" t="n">
+        <v>137.3583</v>
+      </c>
+      <c r="H125" t="n">
+        <v>372.6882</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>173</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,4,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>0.9832</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1.3911</v>
+      </c>
+      <c r="G126" t="n">
+        <v>145.5889</v>
+      </c>
+      <c r="H126" t="n">
+        <v>414.8549</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>174</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2,4,25))</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1.314</v>
+      </c>
+      <c r="G127" t="n">
+        <v>125.0825</v>
+      </c>
+      <c r="H127" t="n">
+        <v>371.7427</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/total.trans.carotene.natif/RANDOMSEARCH_DETAILS_total.trans.carotene.natif.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/total.trans.carotene.natif/RANDOMSEARCH_DETAILS_total.trans.carotene.natif.xlsx
@@ -474,20 +474,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.982</v>
+        <v>0.9831</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3113</v>
+        <v>0.6988</v>
       </c>
       <c r="G2" t="n">
-        <v>140.7441</v>
+        <v>131.1245</v>
       </c>
       <c r="H2" t="n">
-        <v>370.164</v>
+        <v>355.4137</v>
       </c>
     </row>
     <row r="3">
@@ -506,20 +506,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9875</v>
+        <v>0.9785</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3344</v>
+        <v>0.6432</v>
       </c>
       <c r="G3" t="n">
-        <v>129.7832</v>
+        <v>159.8005</v>
       </c>
       <c r="H3" t="n">
-        <v>383.6347</v>
+        <v>386.8057</v>
       </c>
     </row>
     <row r="4">
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.981</v>
+        <v>0.9746</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4078</v>
+        <v>0.5766</v>
       </c>
       <c r="G4" t="n">
-        <v>151.7454</v>
+        <v>163.1577</v>
       </c>
       <c r="H4" t="n">
-        <v>423.6192</v>
+        <v>421.3678</v>
       </c>
     </row>
     <row r="5">
@@ -570,20 +570,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.8381</v>
+        <v>0.775</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0031</v>
+        <v>0.0038</v>
       </c>
       <c r="G5" t="n">
-        <v>398.576</v>
+        <v>451.4814</v>
       </c>
       <c r="H5" t="n">
-        <v>664.4082</v>
+        <v>646.3641</v>
       </c>
     </row>
     <row r="6">
@@ -602,20 +602,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.8228</v>
+        <v>0.7783</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9864</v>
+        <v>0.0182</v>
       </c>
       <c r="G6" t="n">
-        <v>412.1131</v>
+        <v>447.6021</v>
       </c>
       <c r="H6" t="n">
-        <v>658.8523</v>
+        <v>641.676</v>
       </c>
     </row>
     <row r="7">
@@ -634,20 +634,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.97</v>
+        <v>0.9426</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4213</v>
+        <v>0.5216</v>
       </c>
       <c r="G7" t="n">
-        <v>174.3909</v>
+        <v>229.9965</v>
       </c>
       <c r="H7" t="n">
-        <v>430.6083</v>
+        <v>447.9171</v>
       </c>
     </row>
     <row r="8">
@@ -666,20 +666,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.9504</v>
+        <v>0.9356</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4168</v>
+        <v>0.5573</v>
       </c>
       <c r="G8" t="n">
-        <v>218.2784</v>
+        <v>238.3966</v>
       </c>
       <c r="H8" t="n">
-        <v>428.3029</v>
+        <v>430.8976</v>
       </c>
     </row>
     <row r="9">
@@ -698,20 +698,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9885</v>
+        <v>0.9863</v>
       </c>
       <c r="F9" t="n">
-        <v>1.308</v>
+        <v>0.6662</v>
       </c>
       <c r="G9" t="n">
-        <v>128.9592</v>
+        <v>132.5343</v>
       </c>
       <c r="H9" t="n">
-        <v>368.1915</v>
+        <v>374.1316</v>
       </c>
     </row>
     <row r="10">
@@ -730,20 +730,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9715</v>
+        <v>0.9337</v>
       </c>
       <c r="F10" t="n">
-        <v>1.443</v>
+        <v>0.5416</v>
       </c>
       <c r="G10" t="n">
-        <v>174.2967</v>
+        <v>243.1038</v>
       </c>
       <c r="H10" t="n">
-        <v>441.5528</v>
+        <v>438.4662</v>
       </c>
     </row>
     <row r="11">
@@ -762,20 +762,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9777</v>
+        <v>0.9477</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4504</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>158.0648</v>
+        <v>216.7185</v>
       </c>
       <c r="H11" t="n">
-        <v>445.2347</v>
+        <v>438.3307</v>
       </c>
     </row>
     <row r="12">
@@ -794,20 +794,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9497</v>
+        <v>0.9335</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4494</v>
+        <v>0.5474</v>
       </c>
       <c r="G12" t="n">
-        <v>220.1589</v>
+        <v>243.0118</v>
       </c>
       <c r="H12" t="n">
-        <v>444.7286</v>
+        <v>435.6567</v>
       </c>
     </row>
     <row r="13">
@@ -826,20 +826,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9383</v>
+        <v>0.9336</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4508</v>
+        <v>0.5401</v>
       </c>
       <c r="G13" t="n">
-        <v>240.2028</v>
+        <v>243.2472</v>
       </c>
       <c r="H13" t="n">
-        <v>445.4274</v>
+        <v>439.1544</v>
       </c>
     </row>
     <row r="14">
@@ -858,20 +858,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9364</v>
+        <v>0.9329</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4492</v>
+        <v>0.5401</v>
       </c>
       <c r="G14" t="n">
-        <v>243.4965</v>
+        <v>243.9598</v>
       </c>
       <c r="H14" t="n">
-        <v>444.645</v>
+        <v>439.1699</v>
       </c>
     </row>
     <row r="15">
@@ -890,20 +890,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9485</v>
+        <v>0.9339</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4506</v>
+        <v>0.5435</v>
       </c>
       <c r="G15" t="n">
-        <v>222.9272</v>
+        <v>243.0397</v>
       </c>
       <c r="H15" t="n">
-        <v>445.3399</v>
+        <v>437.5166</v>
       </c>
     </row>
     <row r="16">
@@ -922,20 +922,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9362</v>
+        <v>0.9522</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4559</v>
+        <v>0.544</v>
       </c>
       <c r="G16" t="n">
-        <v>244.363</v>
+        <v>207.5299</v>
       </c>
       <c r="H16" t="n">
-        <v>447.95</v>
+        <v>437.28</v>
       </c>
     </row>
     <row r="17">
@@ -954,20 +954,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9364</v>
+        <v>0.9514</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4543</v>
+        <v>0.5385</v>
       </c>
       <c r="G17" t="n">
-        <v>243.8387</v>
+        <v>209.0679</v>
       </c>
       <c r="H17" t="n">
-        <v>447.1251</v>
+        <v>439.9451</v>
       </c>
     </row>
     <row r="18">
@@ -990,16 +990,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9843</v>
+        <v>0.977</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3264</v>
+        <v>0.6794</v>
       </c>
       <c r="G18" t="n">
-        <v>130.0626</v>
+        <v>147.5223</v>
       </c>
       <c r="H18" t="n">
-        <v>378.9852</v>
+        <v>366.6474</v>
       </c>
     </row>
     <row r="19">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9819</v>
+        <v>0.981</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3158</v>
+        <v>0.6738</v>
       </c>
       <c r="G19" t="n">
-        <v>135.9049</v>
+        <v>141.4898</v>
       </c>
       <c r="H19" t="n">
-        <v>372.8124</v>
+        <v>369.8776</v>
       </c>
     </row>
     <row r="20">
@@ -1050,20 +1050,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9795</v>
+        <v>0.9798</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3173</v>
+        <v>0.6592</v>
       </c>
       <c r="G20" t="n">
-        <v>145.4921</v>
+        <v>143.4415</v>
       </c>
       <c r="H20" t="n">
-        <v>373.6858</v>
+        <v>378.0536</v>
       </c>
     </row>
     <row r="21">
@@ -1082,20 +1082,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.977</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3079</v>
+        <v>0.6675</v>
       </c>
       <c r="G21" t="n">
-        <v>126.8036</v>
+        <v>148.5089</v>
       </c>
       <c r="H21" t="n">
-        <v>368.0905</v>
+        <v>373.4036</v>
       </c>
     </row>
     <row r="22">
@@ -1114,20 +1114,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9858</v>
+        <v>0.9797</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2992</v>
+        <v>0.6797</v>
       </c>
       <c r="G22" t="n">
-        <v>125.6142</v>
+        <v>141.0124</v>
       </c>
       <c r="H22" t="n">
-        <v>362.8445</v>
+        <v>366.4894</v>
       </c>
     </row>
     <row r="23">
@@ -1146,20 +1146,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9851</v>
+        <v>0.9786</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3119</v>
+        <v>0.6634</v>
       </c>
       <c r="G23" t="n">
-        <v>128.1761</v>
+        <v>147.1065</v>
       </c>
       <c r="H23" t="n">
-        <v>370.5051</v>
+        <v>375.6911</v>
       </c>
     </row>
     <row r="24">
@@ -1178,20 +1178,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.979</v>
+        <v>0.9792</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3035</v>
+        <v>0.6534</v>
       </c>
       <c r="G24" t="n">
-        <v>150.1747</v>
+        <v>144.6747</v>
       </c>
       <c r="H24" t="n">
-        <v>365.4631</v>
+        <v>381.2646</v>
       </c>
     </row>
     <row r="25">
@@ -1210,20 +1210,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9841</v>
+        <v>0.9717</v>
       </c>
       <c r="F25" t="n">
-        <v>1.3027</v>
+        <v>0.661</v>
       </c>
       <c r="G25" t="n">
-        <v>130.2113</v>
+        <v>169.3451</v>
       </c>
       <c r="H25" t="n">
-        <v>365.0037</v>
+        <v>377.023</v>
       </c>
     </row>
     <row r="26">
@@ -1246,16 +1246,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9851</v>
+        <v>0.9808</v>
       </c>
       <c r="F26" t="n">
-        <v>1.315</v>
+        <v>0.6835</v>
       </c>
       <c r="G26" t="n">
-        <v>126.3311</v>
+        <v>136.3937</v>
       </c>
       <c r="H26" t="n">
-        <v>372.3351</v>
+        <v>364.3449</v>
       </c>
     </row>
     <row r="27">
@@ -1274,20 +1274,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9849</v>
+        <v>0.9764</v>
       </c>
       <c r="F27" t="n">
-        <v>1.3264</v>
+        <v>0.68</v>
       </c>
       <c r="G27" t="n">
-        <v>131.0795</v>
+        <v>148.2854</v>
       </c>
       <c r="H27" t="n">
-        <v>378.9793</v>
+        <v>366.3221</v>
       </c>
     </row>
     <row r="28">
@@ -1310,16 +1310,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.984</v>
+        <v>0.9784</v>
       </c>
       <c r="F28" t="n">
-        <v>1.3106</v>
+        <v>0.6714</v>
       </c>
       <c r="G28" t="n">
-        <v>131.4122</v>
+        <v>143.79</v>
       </c>
       <c r="H28" t="n">
-        <v>369.7393</v>
+        <v>371.2071</v>
       </c>
     </row>
     <row r="29">
@@ -1342,16 +1342,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.985</v>
+        <v>0.9805</v>
       </c>
       <c r="F29" t="n">
-        <v>1.3227</v>
+        <v>0.6645</v>
       </c>
       <c r="G29" t="n">
-        <v>131.0279</v>
+        <v>142.2323</v>
       </c>
       <c r="H29" t="n">
-        <v>376.8445</v>
+        <v>375.0708</v>
       </c>
     </row>
     <row r="30">
@@ -1370,20 +1370,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9849</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>1.3101</v>
+        <v>0.67</v>
       </c>
       <c r="G30" t="n">
-        <v>129.2158</v>
+        <v>147.6927</v>
       </c>
       <c r="H30" t="n">
-        <v>369.4271</v>
+        <v>371.9892</v>
       </c>
     </row>
     <row r="31">
@@ -1402,20 +1402,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9849</v>
+        <v>0.9785</v>
       </c>
       <c r="F31" t="n">
-        <v>1.3145</v>
+        <v>0.6666</v>
       </c>
       <c r="G31" t="n">
-        <v>129.1021</v>
+        <v>145.6788</v>
       </c>
       <c r="H31" t="n">
-        <v>372.0269</v>
+        <v>373.927</v>
       </c>
     </row>
     <row r="32">
@@ -1434,20 +1434,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9855</v>
+        <v>0.9828</v>
       </c>
       <c r="F32" t="n">
-        <v>1.3044</v>
+        <v>0.6677</v>
       </c>
       <c r="G32" t="n">
-        <v>127.3325</v>
+        <v>134.6373</v>
       </c>
       <c r="H32" t="n">
-        <v>366.0345</v>
+        <v>373.2924</v>
       </c>
     </row>
     <row r="33">
@@ -1466,20 +1466,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9856</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>1.3133</v>
+        <v>0.6692</v>
       </c>
       <c r="G33" t="n">
-        <v>127.051</v>
+        <v>166.406</v>
       </c>
       <c r="H33" t="n">
-        <v>371.3089</v>
+        <v>372.4603</v>
       </c>
     </row>
     <row r="34">
@@ -1498,20 +1498,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9765</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>1.3586</v>
+        <v>0.6157</v>
       </c>
       <c r="G34" t="n">
-        <v>168.4107</v>
+        <v>156.6744</v>
       </c>
       <c r="H34" t="n">
-        <v>397.2605</v>
+        <v>401.4675</v>
       </c>
     </row>
     <row r="35">
@@ -1530,20 +1530,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9868</v>
+        <v>0.9822</v>
       </c>
       <c r="F35" t="n">
-        <v>1.3466</v>
+        <v>0.6232</v>
       </c>
       <c r="G35" t="n">
-        <v>133.9053</v>
+        <v>155.1666</v>
       </c>
       <c r="H35" t="n">
-        <v>390.5407</v>
+        <v>397.5042</v>
       </c>
     </row>
     <row r="36">
@@ -1566,16 +1566,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.987</v>
+        <v>0.9859</v>
       </c>
       <c r="F36" t="n">
-        <v>1.324</v>
+        <v>0.6502</v>
       </c>
       <c r="G36" t="n">
-        <v>129.3663</v>
+        <v>132.9296</v>
       </c>
       <c r="H36" t="n">
-        <v>377.6252</v>
+        <v>382.9797</v>
       </c>
     </row>
     <row r="37">
@@ -1594,20 +1594,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9876</v>
+        <v>0.9835</v>
       </c>
       <c r="F37" t="n">
-        <v>1.3175</v>
+        <v>0.6746</v>
       </c>
       <c r="G37" t="n">
-        <v>124.7023</v>
+        <v>136.8031</v>
       </c>
       <c r="H37" t="n">
-        <v>373.8045</v>
+        <v>369.4294</v>
       </c>
     </row>
     <row r="38">
@@ -1626,20 +1626,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.9802</v>
+        <v>0.9823</v>
       </c>
       <c r="F38" t="n">
-        <v>1.3053</v>
+        <v>0.6757</v>
       </c>
       <c r="G38" t="n">
-        <v>156.887</v>
+        <v>140.7205</v>
       </c>
       <c r="H38" t="n">
-        <v>366.5286</v>
+        <v>368.7835</v>
       </c>
     </row>
     <row r="39">
@@ -1658,20 +1658,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.9861</v>
+        <v>0.9776</v>
       </c>
       <c r="F39" t="n">
-        <v>1.3147</v>
+        <v>0.6733</v>
       </c>
       <c r="G39" t="n">
-        <v>126.6765</v>
+        <v>154.4107</v>
       </c>
       <c r="H39" t="n">
-        <v>372.1749</v>
+        <v>370.1164</v>
       </c>
     </row>
     <row r="40">
@@ -1694,16 +1694,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9826</v>
       </c>
       <c r="F40" t="n">
-        <v>1.3174</v>
+        <v>0.67</v>
       </c>
       <c r="G40" t="n">
-        <v>133.1028</v>
+        <v>136.8099</v>
       </c>
       <c r="H40" t="n">
-        <v>373.7714</v>
+        <v>372.0138</v>
       </c>
     </row>
     <row r="41">
@@ -1722,20 +1722,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9769</v>
+        <v>0.9776</v>
       </c>
       <c r="F41" t="n">
-        <v>1.3589</v>
+        <v>0.6123</v>
       </c>
       <c r="G41" t="n">
-        <v>167.9518</v>
+        <v>158.0663</v>
       </c>
       <c r="H41" t="n">
-        <v>397.4093</v>
+        <v>403.2227</v>
       </c>
     </row>
     <row r="42">
@@ -1754,20 +1754,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9867</v>
+        <v>0.9782</v>
       </c>
       <c r="F42" t="n">
-        <v>1.3472</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>134.4413</v>
+        <v>164.5595</v>
       </c>
       <c r="H42" t="n">
-        <v>390.8835</v>
+        <v>398.9392</v>
       </c>
     </row>
     <row r="43">
@@ -1790,16 +1790,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9871</v>
+        <v>0.9859</v>
       </c>
       <c r="F43" t="n">
-        <v>1.3266</v>
+        <v>0.6506</v>
       </c>
       <c r="G43" t="n">
-        <v>129.1184</v>
+        <v>133.0974</v>
       </c>
       <c r="H43" t="n">
-        <v>379.147</v>
+        <v>382.8017</v>
       </c>
     </row>
     <row r="44">
@@ -1818,20 +1818,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9869</v>
+        <v>0.9779</v>
       </c>
       <c r="F44" t="n">
-        <v>1.3121</v>
+        <v>0.6731</v>
       </c>
       <c r="G44" t="n">
-        <v>127.8132</v>
+        <v>154.6937</v>
       </c>
       <c r="H44" t="n">
-        <v>370.6106</v>
+        <v>370.2461</v>
       </c>
     </row>
     <row r="45">
@@ -1850,20 +1850,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9801</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>1.2993</v>
+        <v>0.674</v>
       </c>
       <c r="G45" t="n">
-        <v>156.2138</v>
+        <v>141.2902</v>
       </c>
       <c r="H45" t="n">
-        <v>362.9135</v>
+        <v>369.7624</v>
       </c>
     </row>
     <row r="46">
@@ -1882,20 +1882,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9862</v>
+        <v>0.9837</v>
       </c>
       <c r="F46" t="n">
-        <v>1.3181</v>
+        <v>0.6788</v>
       </c>
       <c r="G46" t="n">
-        <v>126.0829</v>
+        <v>137.1434</v>
       </c>
       <c r="H46" t="n">
-        <v>374.1761</v>
+        <v>366.9929</v>
       </c>
     </row>
     <row r="47">
@@ -1914,20 +1914,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9782</v>
+        <v>0.9827</v>
       </c>
       <c r="F47" t="n">
-        <v>1.3237</v>
+        <v>0.6676</v>
       </c>
       <c r="G47" t="n">
-        <v>158.3174</v>
+        <v>137.3374</v>
       </c>
       <c r="H47" t="n">
-        <v>377.4575</v>
+        <v>373.3834</v>
       </c>
     </row>
     <row r="48">
@@ -1950,16 +1950,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.9859</v>
+        <v>0.9839</v>
       </c>
       <c r="F48" t="n">
-        <v>1.3407</v>
+        <v>0.6308</v>
       </c>
       <c r="G48" t="n">
-        <v>135.8183</v>
+        <v>142.2406</v>
       </c>
       <c r="H48" t="n">
-        <v>387.2409</v>
+        <v>393.5086</v>
       </c>
     </row>
     <row r="49">
@@ -1978,20 +1978,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.9868</v>
+        <v>0.9817</v>
       </c>
       <c r="F49" t="n">
-        <v>1.3173</v>
+        <v>0.6508</v>
       </c>
       <c r="G49" t="n">
-        <v>131.0246</v>
+        <v>143.9534</v>
       </c>
       <c r="H49" t="n">
-        <v>373.697</v>
+        <v>382.6711</v>
       </c>
     </row>
     <row r="50">
@@ -2014,16 +2014,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.9303</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="F50" t="n">
-        <v>1.8437</v>
+        <v>0.0675</v>
       </c>
       <c r="G50" t="n">
-        <v>312.4229</v>
+        <v>326.8589</v>
       </c>
       <c r="H50" t="n">
-        <v>609.3537</v>
+        <v>625.3321</v>
       </c>
     </row>
     <row r="51">
@@ -2042,20 +2042,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.8963</v>
+        <v>0.8528</v>
       </c>
       <c r="F51" t="n">
-        <v>1.881</v>
+        <v>0.0273</v>
       </c>
       <c r="G51" t="n">
-        <v>369.8412</v>
+        <v>418.6779</v>
       </c>
       <c r="H51" t="n">
-        <v>622.6793</v>
+        <v>638.6958</v>
       </c>
     </row>
     <row r="52">
@@ -2074,20 +2074,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.8874</v>
+        <v>0.8656</v>
       </c>
       <c r="F52" t="n">
-        <v>1.8833</v>
+        <v>0.0321</v>
       </c>
       <c r="G52" t="n">
-        <v>374.7844</v>
+        <v>404.9454</v>
       </c>
       <c r="H52" t="n">
-        <v>623.4897999999999</v>
+        <v>637.095</v>
       </c>
     </row>
     <row r="53">
@@ -2106,20 +2106,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.9127</v>
+        <v>0.8929</v>
       </c>
       <c r="F53" t="n">
-        <v>1.8622</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>356.8295</v>
+        <v>387.0897</v>
       </c>
       <c r="H53" t="n">
-        <v>616.0087</v>
+        <v>621.7417</v>
       </c>
     </row>
     <row r="54">
@@ -2138,20 +2138,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.9117</v>
       </c>
       <c r="F54" t="n">
-        <v>1.8379</v>
+        <v>0.1053</v>
       </c>
       <c r="G54" t="n">
-        <v>362.0448</v>
+        <v>337.7864</v>
       </c>
       <c r="H54" t="n">
-        <v>607.2488</v>
+        <v>612.5371</v>
       </c>
     </row>
     <row r="55">
@@ -2170,20 +2170,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.973</v>
+        <v>0.8893</v>
       </c>
       <c r="F55" t="n">
-        <v>1.9205</v>
+        <v>-0.0014</v>
       </c>
       <c r="G55" t="n">
-        <v>233.3946</v>
+        <v>410.7427</v>
       </c>
       <c r="H55" t="n">
-        <v>636.4865</v>
+        <v>648.0345</v>
       </c>
     </row>
     <row r="56">
@@ -2202,20 +2202,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.9764</v>
+        <v>0.9181</v>
       </c>
       <c r="F56" t="n">
-        <v>1.9141</v>
+        <v>0.0106</v>
       </c>
       <c r="G56" t="n">
-        <v>233.3864</v>
+        <v>396.4376</v>
       </c>
       <c r="H56" t="n">
-        <v>634.2611000000001</v>
+        <v>644.1376</v>
       </c>
     </row>
     <row r="57">
@@ -2234,20 +2234,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.9113</v>
+        <v>0.9026999999999999</v>
       </c>
       <c r="F57" t="n">
-        <v>1.902</v>
+        <v>0.0311</v>
       </c>
       <c r="G57" t="n">
-        <v>357.056</v>
+        <v>389.7473</v>
       </c>
       <c r="H57" t="n">
-        <v>630.0482</v>
+        <v>637.421</v>
       </c>
     </row>
     <row r="58">
@@ -2266,20 +2266,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.8209</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>1.9874</v>
+        <v>0.0178</v>
       </c>
       <c r="G58" t="n">
-        <v>412.9541</v>
+        <v>447.9897</v>
       </c>
       <c r="H58" t="n">
-        <v>659.1869</v>
+        <v>641.8047</v>
       </c>
     </row>
     <row r="59">
@@ -2298,20 +2298,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.8274</v>
+        <v>0.7783</v>
       </c>
       <c r="F59" t="n">
-        <v>1.9887</v>
+        <v>0.0165</v>
       </c>
       <c r="G59" t="n">
-        <v>408.9831</v>
+        <v>447.6094</v>
       </c>
       <c r="H59" t="n">
-        <v>659.6507</v>
+        <v>642.229</v>
       </c>
     </row>
     <row r="60">
@@ -2330,20 +2330,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.8288</v>
+        <v>0.7768</v>
       </c>
       <c r="F60" t="n">
-        <v>1.9812</v>
+        <v>0.0186</v>
       </c>
       <c r="G60" t="n">
-        <v>407.2439</v>
+        <v>448.0139</v>
       </c>
       <c r="H60" t="n">
-        <v>657.1375</v>
+        <v>641.5429</v>
       </c>
     </row>
     <row r="61">
@@ -2362,20 +2362,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.8282</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="F61" t="n">
-        <v>1.9925</v>
+        <v>0.0208</v>
       </c>
       <c r="G61" t="n">
-        <v>405.9075</v>
+        <v>447.6296</v>
       </c>
       <c r="H61" t="n">
-        <v>660.8886</v>
+        <v>640.8288</v>
       </c>
     </row>
     <row r="62">
@@ -2394,20 +2394,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.838</v>
+        <v>0.8661</v>
       </c>
       <c r="F62" t="n">
-        <v>1.927</v>
+        <v>0.0648</v>
       </c>
       <c r="G62" t="n">
-        <v>418.1797</v>
+        <v>391.2323</v>
       </c>
       <c r="H62" t="n">
-        <v>638.7118</v>
+        <v>626.2403</v>
       </c>
     </row>
     <row r="63">
@@ -2426,20 +2426,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.8354</v>
+        <v>0.8632</v>
       </c>
       <c r="F63" t="n">
-        <v>1.9225</v>
+        <v>0.0815</v>
       </c>
       <c r="G63" t="n">
-        <v>419.0805</v>
+        <v>387.5046</v>
       </c>
       <c r="H63" t="n">
-        <v>637.1592000000001</v>
+        <v>620.6464999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2458,20 +2458,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.8287</v>
+        <v>0.8656</v>
       </c>
       <c r="F64" t="n">
-        <v>1.9186</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="G64" t="n">
-        <v>419.602</v>
+        <v>384.749</v>
       </c>
       <c r="H64" t="n">
-        <v>635.8348999999999</v>
+        <v>620.7357</v>
       </c>
     </row>
     <row r="65">
@@ -2490,20 +2490,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.8227</v>
+        <v>0.8488</v>
       </c>
       <c r="F65" t="n">
-        <v>1.9343</v>
+        <v>0.0853</v>
       </c>
       <c r="G65" t="n">
-        <v>421.583</v>
+        <v>395.8653</v>
       </c>
       <c r="H65" t="n">
-        <v>641.2296</v>
+        <v>619.3541</v>
       </c>
     </row>
     <row r="66">
@@ -2522,20 +2522,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.9016</v>
+        <v>0.8849</v>
       </c>
       <c r="F66" t="n">
-        <v>1.9156</v>
+        <v>0.0314</v>
       </c>
       <c r="G66" t="n">
-        <v>364.3609</v>
+        <v>409.604</v>
       </c>
       <c r="H66" t="n">
-        <v>634.7954</v>
+        <v>637.328</v>
       </c>
     </row>
     <row r="67">
@@ -2554,20 +2554,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.8952</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="F67" t="n">
-        <v>1.8947</v>
+        <v>0.051</v>
       </c>
       <c r="G67" t="n">
-        <v>372.2366</v>
+        <v>407.6881</v>
       </c>
       <c r="H67" t="n">
-        <v>627.5069</v>
+        <v>630.8646</v>
       </c>
     </row>
     <row r="68">
@@ -2586,20 +2586,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.8956</v>
+        <v>0.8796</v>
       </c>
       <c r="F68" t="n">
-        <v>1.9194</v>
+        <v>0.0409</v>
       </c>
       <c r="G68" t="n">
-        <v>380.4722</v>
+        <v>410.4392</v>
       </c>
       <c r="H68" t="n">
-        <v>636.0913</v>
+        <v>634.1900000000001</v>
       </c>
     </row>
     <row r="69">
@@ -2618,20 +2618,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9802</v>
+        <v>0.9581</v>
       </c>
       <c r="F69" t="n">
-        <v>1.3269</v>
+        <v>0.6587</v>
       </c>
       <c r="G69" t="n">
-        <v>147.2465</v>
+        <v>199.4698</v>
       </c>
       <c r="H69" t="n">
-        <v>379.3111</v>
+        <v>378.3144</v>
       </c>
     </row>
     <row r="70">
@@ -2650,20 +2650,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9821</v>
+        <v>0.9818</v>
       </c>
       <c r="F70" t="n">
-        <v>1.2998</v>
+        <v>0.6872</v>
       </c>
       <c r="G70" t="n">
-        <v>139.5488</v>
+        <v>139.0121</v>
       </c>
       <c r="H70" t="n">
-        <v>363.2622</v>
+        <v>362.169</v>
       </c>
     </row>
     <row r="71">
@@ -2682,20 +2682,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9839</v>
+        <v>0.9789</v>
       </c>
       <c r="F71" t="n">
-        <v>1.3323</v>
+        <v>0.6493</v>
       </c>
       <c r="G71" t="n">
-        <v>133.6539</v>
+        <v>145.1454</v>
       </c>
       <c r="H71" t="n">
-        <v>382.3925</v>
+        <v>383.491</v>
       </c>
     </row>
     <row r="72">
@@ -2714,20 +2714,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.985</v>
+        <v>0.9749</v>
       </c>
       <c r="F72" t="n">
-        <v>1.3141</v>
+        <v>0.6488</v>
       </c>
       <c r="G72" t="n">
-        <v>128.1703</v>
+        <v>158.1766</v>
       </c>
       <c r="H72" t="n">
-        <v>371.7926</v>
+        <v>383.7944</v>
       </c>
     </row>
     <row r="73">
@@ -2750,16 +2750,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.9851</v>
+        <v>0.9825</v>
       </c>
       <c r="F73" t="n">
-        <v>1.3573</v>
+        <v>0.6025</v>
       </c>
       <c r="G73" t="n">
-        <v>140.5687</v>
+        <v>147.5778</v>
       </c>
       <c r="H73" t="n">
-        <v>396.5206</v>
+        <v>408.2771</v>
       </c>
     </row>
     <row r="74">
@@ -2778,20 +2778,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9857</v>
+        <v>0.9717</v>
       </c>
       <c r="F74" t="n">
-        <v>1.3243</v>
+        <v>0.6669</v>
       </c>
       <c r="G74" t="n">
-        <v>132.9789</v>
+        <v>167.4188</v>
       </c>
       <c r="H74" t="n">
-        <v>377.7863</v>
+        <v>373.7718</v>
       </c>
     </row>
     <row r="75">
@@ -2810,20 +2810,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.9827</v>
+        <v>0.9525</v>
       </c>
       <c r="F75" t="n">
-        <v>1.3891</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="G75" t="n">
-        <v>138.5767</v>
+        <v>208.2783</v>
       </c>
       <c r="H75" t="n">
-        <v>413.7852</v>
+        <v>415.5774</v>
       </c>
     </row>
     <row r="76">
@@ -2842,20 +2842,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.9827</v>
+        <v>0.9525</v>
       </c>
       <c r="F76" t="n">
-        <v>1.3891</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="G76" t="n">
-        <v>138.5767</v>
+        <v>208.2783</v>
       </c>
       <c r="H76" t="n">
-        <v>413.7852</v>
+        <v>415.5774</v>
       </c>
     </row>
     <row r="77">
@@ -2874,20 +2874,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.8478</v>
       </c>
       <c r="F77" t="n">
-        <v>1.9257</v>
+        <v>0.0212</v>
       </c>
       <c r="G77" t="n">
-        <v>395.3523</v>
+        <v>396.1434</v>
       </c>
       <c r="H77" t="n">
-        <v>638.2849</v>
+        <v>640.6694</v>
       </c>
     </row>
     <row r="78">
@@ -2906,20 +2906,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.8555</v>
+        <v>0.8451</v>
       </c>
       <c r="F78" t="n">
-        <v>1.9321</v>
+        <v>0.0279</v>
       </c>
       <c r="G78" t="n">
-        <v>393.5737</v>
+        <v>398.4286</v>
       </c>
       <c r="H78" t="n">
-        <v>640.4891</v>
+        <v>638.4899</v>
       </c>
     </row>
     <row r="79">
@@ -2938,20 +2938,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.8537</v>
+        <v>0.8445</v>
       </c>
       <c r="F79" t="n">
-        <v>1.9298</v>
+        <v>0.0226</v>
       </c>
       <c r="G79" t="n">
-        <v>394.4773</v>
+        <v>399.0101</v>
       </c>
       <c r="H79" t="n">
-        <v>639.6693</v>
+        <v>640.239</v>
       </c>
     </row>
     <row r="80">
@@ -2970,20 +2970,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.8556</v>
+        <v>0.8449</v>
       </c>
       <c r="F80" t="n">
-        <v>1.9305</v>
+        <v>0.0273</v>
       </c>
       <c r="G80" t="n">
-        <v>392.8552</v>
+        <v>398.5727</v>
       </c>
       <c r="H80" t="n">
-        <v>639.9406</v>
+        <v>638.6942</v>
       </c>
     </row>
     <row r="81">
@@ -3002,20 +3002,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.8983</v>
+        <v>0.8427</v>
       </c>
       <c r="F81" t="n">
-        <v>1.9203</v>
+        <v>0.0178</v>
       </c>
       <c r="G81" t="n">
-        <v>366.4063</v>
+        <v>427.4668</v>
       </c>
       <c r="H81" t="n">
-        <v>636.4066</v>
+        <v>641.8049999999999</v>
       </c>
     </row>
     <row r="82">
@@ -3034,20 +3034,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.9213</v>
+        <v>0.8616</v>
       </c>
       <c r="F82" t="n">
-        <v>1.9218</v>
+        <v>0.0198</v>
       </c>
       <c r="G82" t="n">
-        <v>322.5342</v>
+        <v>411.4251</v>
       </c>
       <c r="H82" t="n">
-        <v>636.9181</v>
+        <v>641.1452</v>
       </c>
     </row>
     <row r="83">
@@ -3066,20 +3066,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.9823</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="F83" t="n">
-        <v>1.3891</v>
+        <v>0.58</v>
       </c>
       <c r="G83" t="n">
-        <v>135.7459</v>
+        <v>210.6591</v>
       </c>
       <c r="H83" t="n">
-        <v>413.7923</v>
+        <v>419.7053</v>
       </c>
     </row>
     <row r="84">
@@ -3098,20 +3098,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.9849</v>
+        <v>0.9522</v>
       </c>
       <c r="F84" t="n">
-        <v>1.386</v>
+        <v>0.5784</v>
       </c>
       <c r="G84" t="n">
-        <v>128.8765</v>
+        <v>208.3429</v>
       </c>
       <c r="H84" t="n">
-        <v>412.1432</v>
+        <v>420.5041</v>
       </c>
     </row>
     <row r="85">
@@ -3130,20 +3130,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.9818</v>
+        <v>0.9508</v>
       </c>
       <c r="F85" t="n">
-        <v>1.3877</v>
+        <v>0.5816</v>
       </c>
       <c r="G85" t="n">
-        <v>137.3948</v>
+        <v>211.3379</v>
       </c>
       <c r="H85" t="n">
-        <v>413.0682</v>
+        <v>418.8864</v>
       </c>
     </row>
     <row r="86">
@@ -3162,20 +3162,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9858</v>
+        <v>0.9801</v>
       </c>
       <c r="F86" t="n">
-        <v>1.3111</v>
+        <v>0.6681</v>
       </c>
       <c r="G86" t="n">
-        <v>122.6694</v>
+        <v>145.7355</v>
       </c>
       <c r="H86" t="n">
-        <v>370.0113</v>
+        <v>373.1035</v>
       </c>
     </row>
     <row r="87">
@@ -3194,20 +3194,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9807</v>
+        <v>0.9769</v>
       </c>
       <c r="F87" t="n">
-        <v>1.3215</v>
+        <v>0.6714</v>
       </c>
       <c r="G87" t="n">
-        <v>142.8131</v>
+        <v>147.6051</v>
       </c>
       <c r="H87" t="n">
-        <v>376.1407</v>
+        <v>371.2272</v>
       </c>
     </row>
     <row r="88">
@@ -3226,20 +3226,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.9861</v>
+        <v>0.9744</v>
       </c>
       <c r="F88" t="n">
-        <v>1.3212</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>122.1792</v>
+        <v>161.1094</v>
       </c>
       <c r="H88" t="n">
-        <v>375.95</v>
+        <v>377.1587</v>
       </c>
     </row>
     <row r="89">
@@ -3258,20 +3258,20 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9855</v>
+        <v>0.9748</v>
       </c>
       <c r="F89" t="n">
-        <v>1.3189</v>
+        <v>0.6777</v>
       </c>
       <c r="G89" t="n">
-        <v>124.18</v>
+        <v>153.5695</v>
       </c>
       <c r="H89" t="n">
-        <v>374.6143</v>
+        <v>367.653</v>
       </c>
     </row>
     <row r="90">
@@ -3294,16 +3294,16 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9871</v>
+        <v>0.9859</v>
       </c>
       <c r="F90" t="n">
-        <v>1.3267</v>
+        <v>0.6502</v>
       </c>
       <c r="G90" t="n">
-        <v>129.1657</v>
+        <v>133.0869</v>
       </c>
       <c r="H90" t="n">
-        <v>379.1697</v>
+        <v>383.0203</v>
       </c>
     </row>
     <row r="91">
@@ -3322,20 +3322,20 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9869</v>
+        <v>0.9779</v>
       </c>
       <c r="F91" t="n">
-        <v>1.3121</v>
+        <v>0.6731</v>
       </c>
       <c r="G91" t="n">
-        <v>127.8215</v>
+        <v>154.6937</v>
       </c>
       <c r="H91" t="n">
-        <v>370.593</v>
+        <v>370.2655</v>
       </c>
     </row>
     <row r="92">
@@ -3354,20 +3354,20 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.9861</v>
+        <v>0.9744</v>
       </c>
       <c r="F92" t="n">
-        <v>1.3212</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="G92" t="n">
-        <v>122.1792</v>
+        <v>161.1094</v>
       </c>
       <c r="H92" t="n">
-        <v>375.95</v>
+        <v>377.1587</v>
       </c>
     </row>
     <row r="93">
@@ -3386,20 +3386,20 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9869</v>
+        <v>0.9779</v>
       </c>
       <c r="F93" t="n">
-        <v>1.3121</v>
+        <v>0.6731</v>
       </c>
       <c r="G93" t="n">
-        <v>127.8215</v>
+        <v>154.6937</v>
       </c>
       <c r="H93" t="n">
-        <v>370.593</v>
+        <v>370.2655</v>
       </c>
     </row>
     <row r="94">
@@ -3422,16 +3422,16 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.981</v>
+        <v>0.9746</v>
       </c>
       <c r="F94" t="n">
-        <v>1.4078</v>
+        <v>0.5766</v>
       </c>
       <c r="G94" t="n">
-        <v>151.7454</v>
+        <v>163.1577</v>
       </c>
       <c r="H94" t="n">
-        <v>423.6192</v>
+        <v>421.3678</v>
       </c>
     </row>
     <row r="95">
@@ -3454,16 +3454,16 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.9294</v>
+        <v>0.924</v>
       </c>
       <c r="F95" t="n">
-        <v>2.0964</v>
+        <v>-0.0994</v>
       </c>
       <c r="G95" t="n">
-        <v>337.3206</v>
+        <v>342.734</v>
       </c>
       <c r="H95" t="n">
-        <v>694.6193</v>
+        <v>679.0069</v>
       </c>
     </row>
     <row r="96">
@@ -3482,20 +3482,20 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.9805</v>
+        <v>0.9606</v>
       </c>
       <c r="F96" t="n">
-        <v>1.4113</v>
+        <v>0.5754</v>
       </c>
       <c r="G96" t="n">
-        <v>154.2423</v>
+        <v>194.6526</v>
       </c>
       <c r="H96" t="n">
-        <v>425.4429</v>
+        <v>421.9843</v>
       </c>
     </row>
     <row r="97">
@@ -3514,20 +3514,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.9806</v>
+        <v>0.9167</v>
       </c>
       <c r="F97" t="n">
-        <v>1.4063</v>
+        <v>0.5742</v>
       </c>
       <c r="G97" t="n">
-        <v>155.0043</v>
+        <v>267.4501</v>
       </c>
       <c r="H97" t="n">
-        <v>422.851</v>
+        <v>422.5466</v>
       </c>
     </row>
     <row r="98">
@@ -3550,16 +3550,16 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.9776</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="F98" t="n">
-        <v>1.325</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="G98" t="n">
-        <v>154.5058</v>
+        <v>156.5075</v>
       </c>
       <c r="H98" t="n">
-        <v>378.1848</v>
+        <v>381.6587</v>
       </c>
     </row>
     <row r="99">
@@ -3582,16 +3582,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.9787</v>
+        <v>0.9755</v>
       </c>
       <c r="F99" t="n">
-        <v>1.2945</v>
+        <v>0.6653</v>
       </c>
       <c r="G99" t="n">
-        <v>147.4648</v>
+        <v>154.5481</v>
       </c>
       <c r="H99" t="n">
-        <v>359.9936</v>
+        <v>374.654</v>
       </c>
     </row>
     <row r="100">
@@ -3610,20 +3610,20 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.9777</v>
+        <v>0.9747</v>
       </c>
       <c r="F100" t="n">
-        <v>1.3135</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="G100" t="n">
-        <v>150.8356</v>
+        <v>153.0681</v>
       </c>
       <c r="H100" t="n">
-        <v>371.4181</v>
+        <v>373.2419</v>
       </c>
     </row>
     <row r="101">
@@ -3642,20 +3642,20 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9775</v>
+        <v>0.9784</v>
       </c>
       <c r="F101" t="n">
-        <v>1.306</v>
+        <v>0.655</v>
       </c>
       <c r="G101" t="n">
-        <v>151.8248</v>
+        <v>144.7475</v>
       </c>
       <c r="H101" t="n">
-        <v>366.9511</v>
+        <v>380.3606</v>
       </c>
     </row>
     <row r="102">
@@ -3674,20 +3674,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.9771</v>
+        <v>0.9568</v>
       </c>
       <c r="F102" t="n">
-        <v>1.3163</v>
+        <v>0.6567</v>
       </c>
       <c r="G102" t="n">
-        <v>154.4196</v>
+        <v>199.9659</v>
       </c>
       <c r="H102" t="n">
-        <v>373.1085</v>
+        <v>379.4149</v>
       </c>
     </row>
     <row r="103">
@@ -3706,20 +3706,20 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9846</v>
+        <v>0.9714</v>
       </c>
       <c r="F103" t="n">
-        <v>1.325</v>
+        <v>0.6545</v>
       </c>
       <c r="G103" t="n">
-        <v>132.9983</v>
+        <v>166.6098</v>
       </c>
       <c r="H103" t="n">
-        <v>378.1728</v>
+        <v>380.6409</v>
       </c>
     </row>
     <row r="104">
@@ -3738,20 +3738,20 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.9837</v>
+        <v>0.9708</v>
       </c>
       <c r="F104" t="n">
-        <v>1.3206</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="G104" t="n">
-        <v>136.7633</v>
+        <v>167.998</v>
       </c>
       <c r="H104" t="n">
-        <v>375.6284</v>
+        <v>381.106</v>
       </c>
     </row>
     <row r="105">
@@ -3770,20 +3770,20 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.985</v>
+        <v>0.9796</v>
       </c>
       <c r="F105" t="n">
-        <v>1.29</v>
+        <v>0.6622</v>
       </c>
       <c r="G105" t="n">
-        <v>130.8418</v>
+        <v>145.2787</v>
       </c>
       <c r="H105" t="n">
-        <v>357.2375</v>
+        <v>376.3621</v>
       </c>
     </row>
     <row r="106">
@@ -3802,20 +3802,20 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9836</v>
+        <v>0.9668</v>
       </c>
       <c r="F106" t="n">
-        <v>1.281</v>
+        <v>0.6572</v>
       </c>
       <c r="G106" t="n">
-        <v>132.2536</v>
+        <v>179.1237</v>
       </c>
       <c r="H106" t="n">
-        <v>351.6306</v>
+        <v>379.1421</v>
       </c>
     </row>
     <row r="107">
@@ -3838,16 +3838,16 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.9835</v>
+        <v>0.9779</v>
       </c>
       <c r="F107" t="n">
-        <v>1.2984</v>
+        <v>0.6646</v>
       </c>
       <c r="G107" t="n">
-        <v>133.0067</v>
+        <v>145.6261</v>
       </c>
       <c r="H107" t="n">
-        <v>362.3866</v>
+        <v>375.0255</v>
       </c>
     </row>
     <row r="108">
@@ -3866,20 +3866,20 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.9786</v>
+        <v>0.9711</v>
       </c>
       <c r="F108" t="n">
-        <v>1.3995</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="G108" t="n">
-        <v>166.0339</v>
+        <v>182.8932</v>
       </c>
       <c r="H108" t="n">
-        <v>419.2859</v>
+        <v>403.6856</v>
       </c>
     </row>
     <row r="109">
@@ -3898,20 +3898,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.986</v>
+        <v>0.9826</v>
       </c>
       <c r="F109" t="n">
-        <v>1.3647</v>
+        <v>0.6381</v>
       </c>
       <c r="G109" t="n">
-        <v>138.8048</v>
+        <v>147.4998</v>
       </c>
       <c r="H109" t="n">
-        <v>400.6358</v>
+        <v>389.5787</v>
       </c>
     </row>
     <row r="110">
@@ -3930,20 +3930,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9867</v>
+        <v>0.9818</v>
       </c>
       <c r="F110" t="n">
-        <v>1.3317</v>
+        <v>0.6674</v>
       </c>
       <c r="G110" t="n">
-        <v>132.1723</v>
+        <v>147.038</v>
       </c>
       <c r="H110" t="n">
-        <v>382.0609</v>
+        <v>373.4679</v>
       </c>
     </row>
     <row r="111">
@@ -3962,20 +3962,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9862</v>
+        <v>0.9813</v>
       </c>
       <c r="F111" t="n">
-        <v>1.3268</v>
+        <v>0.6685</v>
       </c>
       <c r="G111" t="n">
-        <v>130.3356</v>
+        <v>145.9956</v>
       </c>
       <c r="H111" t="n">
-        <v>379.2433</v>
+        <v>372.8685</v>
       </c>
     </row>
     <row r="112">
@@ -3994,20 +3994,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9714</v>
       </c>
       <c r="F112" t="n">
-        <v>1.3975</v>
+        <v>0.6111</v>
       </c>
       <c r="G112" t="n">
-        <v>165.9844</v>
+        <v>182.2881</v>
       </c>
       <c r="H112" t="n">
-        <v>418.2393</v>
+        <v>403.8618</v>
       </c>
     </row>
     <row r="113">
@@ -4026,20 +4026,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.9801</v>
+        <v>0.9826</v>
       </c>
       <c r="F113" t="n">
-        <v>1.3651</v>
+        <v>0.6446</v>
       </c>
       <c r="G113" t="n">
-        <v>169.2929</v>
+        <v>148.1421</v>
       </c>
       <c r="H113" t="n">
-        <v>400.8277</v>
+        <v>386.0869</v>
       </c>
     </row>
     <row r="114">
@@ -4058,20 +4058,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9868</v>
+        <v>0.9815</v>
       </c>
       <c r="F114" t="n">
-        <v>1.3304</v>
+        <v>0.6697</v>
       </c>
       <c r="G114" t="n">
-        <v>131.5674</v>
+        <v>147.5174</v>
       </c>
       <c r="H114" t="n">
-        <v>381.3241</v>
+        <v>372.1721</v>
       </c>
     </row>
     <row r="115">
@@ -4094,16 +4094,16 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.986</v>
+        <v>0.9847</v>
       </c>
       <c r="F115" t="n">
-        <v>1.3292</v>
+        <v>0.6634</v>
       </c>
       <c r="G115" t="n">
-        <v>130.3998</v>
+        <v>134.4617</v>
       </c>
       <c r="H115" t="n">
-        <v>380.6561</v>
+        <v>375.6891</v>
       </c>
     </row>
     <row r="116">
@@ -4122,20 +4122,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.9699</v>
+        <v>0.8218</v>
       </c>
       <c r="F116" t="n">
-        <v>1.9243</v>
+        <v>0.0019</v>
       </c>
       <c r="G116" t="n">
-        <v>239.0892</v>
+        <v>440.7631</v>
       </c>
       <c r="H116" t="n">
-        <v>637.7876</v>
+        <v>646.9842</v>
       </c>
     </row>
     <row r="117">
@@ -4154,20 +4154,20 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.9293</v>
+        <v>0.8399</v>
       </c>
       <c r="F117" t="n">
-        <v>1.9494</v>
+        <v>-0.0098</v>
       </c>
       <c r="G117" t="n">
-        <v>316.9833</v>
+        <v>430.1738</v>
       </c>
       <c r="H117" t="n">
-        <v>646.3871</v>
+        <v>650.7613</v>
       </c>
     </row>
     <row r="118">
@@ -4186,20 +4186,20 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.985</v>
+        <v>0.9796</v>
       </c>
       <c r="F118" t="n">
-        <v>1.29</v>
+        <v>0.6622</v>
       </c>
       <c r="G118" t="n">
-        <v>130.8418</v>
+        <v>145.2787</v>
       </c>
       <c r="H118" t="n">
-        <v>357.2375</v>
+        <v>376.3621</v>
       </c>
     </row>
     <row r="119">
@@ -4218,20 +4218,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9801</v>
+        <v>0.9826</v>
       </c>
       <c r="F119" t="n">
-        <v>1.3651</v>
+        <v>0.6446</v>
       </c>
       <c r="G119" t="n">
-        <v>169.2929</v>
+        <v>148.1421</v>
       </c>
       <c r="H119" t="n">
-        <v>400.8277</v>
+        <v>386.0869</v>
       </c>
     </row>
     <row r="120">
@@ -4250,20 +4250,20 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.968</v>
+        <v>0.9729</v>
       </c>
       <c r="F120" t="n">
-        <v>1.3916</v>
+        <v>0.5733</v>
       </c>
       <c r="G120" t="n">
-        <v>179.321</v>
+        <v>162.7276</v>
       </c>
       <c r="H120" t="n">
-        <v>415.1462</v>
+        <v>422.9948</v>
       </c>
     </row>
     <row r="121">
@@ -4282,20 +4282,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.968</v>
+        <v>0.9729</v>
       </c>
       <c r="F121" t="n">
-        <v>1.3916</v>
+        <v>0.5733</v>
       </c>
       <c r="G121" t="n">
-        <v>179.321</v>
+        <v>162.7276</v>
       </c>
       <c r="H121" t="n">
-        <v>415.1462</v>
+        <v>422.9948</v>
       </c>
     </row>
     <row r="122">
@@ -4318,16 +4318,16 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.9858</v>
+        <v>0.9789</v>
       </c>
       <c r="F122" t="n">
-        <v>1.2928</v>
+        <v>0.6717</v>
       </c>
       <c r="G122" t="n">
-        <v>125.518</v>
+        <v>143.8298</v>
       </c>
       <c r="H122" t="n">
-        <v>358.957</v>
+        <v>371.0749</v>
       </c>
     </row>
     <row r="123">
@@ -4346,20 +4346,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.98</v>
+        <v>0.9826</v>
       </c>
       <c r="F123" t="n">
-        <v>1.3661</v>
+        <v>0.6442</v>
       </c>
       <c r="G123" t="n">
-        <v>169.3909</v>
+        <v>148.1444</v>
       </c>
       <c r="H123" t="n">
-        <v>401.3778</v>
+        <v>386.2925</v>
       </c>
     </row>
     <row r="124">
@@ -4378,20 +4378,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9872</v>
+        <v>0.974</v>
       </c>
       <c r="F124" t="n">
-        <v>1.332</v>
+        <v>0.6654</v>
       </c>
       <c r="G124" t="n">
-        <v>130.0281</v>
+        <v>167.2607</v>
       </c>
       <c r="H124" t="n">
-        <v>382.2485</v>
+        <v>374.5754</v>
       </c>
     </row>
     <row r="125">
@@ -4410,20 +4410,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.9821</v>
       </c>
       <c r="F125" t="n">
-        <v>1.3156</v>
+        <v>0.7019</v>
       </c>
       <c r="G125" t="n">
-        <v>137.3583</v>
+        <v>134.2685</v>
       </c>
       <c r="H125" t="n">
-        <v>372.6882</v>
+        <v>353.5498</v>
       </c>
     </row>
     <row r="126">
@@ -4442,20 +4442,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.9832</v>
+        <v>0.9768</v>
       </c>
       <c r="F126" t="n">
-        <v>1.3911</v>
+        <v>0.6024</v>
       </c>
       <c r="G126" t="n">
-        <v>145.5889</v>
+        <v>158.5907</v>
       </c>
       <c r="H126" t="n">
-        <v>414.8549</v>
+        <v>408.3528</v>
       </c>
     </row>
     <row r="127">
@@ -4474,20 +4474,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.988</v>
+        <v>0.9772</v>
       </c>
       <c r="F127" t="n">
-        <v>1.314</v>
+        <v>0.6753</v>
       </c>
       <c r="G127" t="n">
-        <v>125.0825</v>
+        <v>158.8875</v>
       </c>
       <c r="H127" t="n">
-        <v>371.7427</v>
+        <v>369.0364</v>
       </c>
     </row>
   </sheetData>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/total.trans.carotene.natif/RANDOMSEARCH_DETAILS_total.trans.carotene.natif.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/total.trans.carotene.natif/RANDOMSEARCH_DETAILS_total.trans.carotene.natif.xlsx
@@ -2618,7 +2618,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E69" t="n">
